--- a/TDXapp/tdxAppData/dropIndexs.xlsx
+++ b/TDXapp/tdxAppData/dropIndexs.xlsx
@@ -53,337 +53,337 @@
     <t>MarketCode</t>
   </si>
   <si>
+    <t>000902</t>
+  </si>
+  <si>
+    <t>中证流通</t>
+  </si>
+  <si>
+    <t>综合</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>ZZ</t>
+  </si>
+  <si>
+    <t>000985</t>
+  </si>
+  <si>
+    <t>中证全指</t>
+  </si>
+  <si>
+    <t>规模</t>
+  </si>
+  <si>
+    <t>880699</t>
+  </si>
+  <si>
+    <t>最近情绪</t>
+  </si>
+  <si>
+    <t>风格</t>
+  </si>
+  <si>
+    <t>TDXBLK</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>880751</t>
+  </si>
+  <si>
+    <t>昨日跌停</t>
+  </si>
+  <si>
+    <t>880752</t>
+  </si>
+  <si>
+    <t>昨曾跌停</t>
+  </si>
+  <si>
+    <t>880770</t>
+  </si>
+  <si>
+    <t>昨日上榜</t>
+  </si>
+  <si>
+    <t>880774</t>
+  </si>
+  <si>
+    <t>昨日首板</t>
+  </si>
+  <si>
+    <t>880785</t>
+  </si>
+  <si>
+    <t>最近多板</t>
+  </si>
+  <si>
+    <t>880789</t>
+  </si>
+  <si>
+    <t>昨成交20</t>
+  </si>
+  <si>
+    <t>880812</t>
+  </si>
+  <si>
+    <t>昨日连板</t>
+  </si>
+  <si>
+    <t>880863</t>
+  </si>
+  <si>
+    <t>昨日涨停</t>
+  </si>
+  <si>
+    <t>880865</t>
+  </si>
+  <si>
+    <t>近期新高</t>
+  </si>
+  <si>
+    <t>880866</t>
+  </si>
+  <si>
+    <t>近期新低</t>
+  </si>
+  <si>
+    <t>880874</t>
+  </si>
+  <si>
+    <t>昨曾涨停</t>
+  </si>
+  <si>
+    <t>880880</t>
+  </si>
+  <si>
+    <t>近期强势</t>
+  </si>
+  <si>
+    <t>880881</t>
+  </si>
+  <si>
+    <t>近期弱势</t>
+  </si>
+  <si>
+    <t>880884</t>
+  </si>
+  <si>
+    <t>最近异动</t>
+  </si>
+  <si>
+    <t>930655</t>
+  </si>
+  <si>
+    <t>500两倍</t>
+  </si>
+  <si>
+    <t>策略</t>
+  </si>
+  <si>
+    <t>930656</t>
+  </si>
+  <si>
+    <t>500反向</t>
+  </si>
+  <si>
+    <t>930657</t>
+  </si>
+  <si>
+    <t>500反两</t>
+  </si>
+  <si>
+    <t>930715</t>
+  </si>
+  <si>
+    <t>CS朝阳88</t>
+  </si>
+  <si>
+    <t>主题</t>
+  </si>
+  <si>
+    <t>930734</t>
+  </si>
+  <si>
+    <t>360互联+</t>
+  </si>
+  <si>
+    <t>930772</t>
+  </si>
+  <si>
+    <t>100两倍</t>
+  </si>
+  <si>
+    <t>930773</t>
+  </si>
+  <si>
+    <t>100反向</t>
+  </si>
+  <si>
     <t>930774</t>
   </si>
   <si>
     <t>100反两</t>
   </si>
   <si>
-    <t>策略</t>
-  </si>
-  <si>
-    <t>CS</t>
-  </si>
-  <si>
-    <t>EX</t>
-  </si>
-  <si>
-    <t>ZZ</t>
-  </si>
-  <si>
-    <t>930773</t>
-  </si>
-  <si>
-    <t>100反向</t>
-  </si>
-  <si>
-    <t>930772</t>
-  </si>
-  <si>
-    <t>100两倍</t>
+    <t>930903</t>
+  </si>
+  <si>
+    <t>中证A股</t>
+  </si>
+  <si>
+    <t>930994</t>
+  </si>
+  <si>
+    <t>工银股混</t>
+  </si>
+  <si>
+    <t>931228</t>
+  </si>
+  <si>
+    <t>亚洲新兴市场科技</t>
+  </si>
+  <si>
+    <t>931240</t>
+  </si>
+  <si>
+    <t>金选偏股基金</t>
+  </si>
+  <si>
+    <t>931376</t>
+  </si>
+  <si>
+    <t>泰康红利LV</t>
+  </si>
+  <si>
+    <t>931563</t>
+  </si>
+  <si>
+    <t>银华配置</t>
+  </si>
+  <si>
+    <t>931658</t>
+  </si>
+  <si>
+    <t>中邮理财稳健策略</t>
+  </si>
+  <si>
+    <t>931659</t>
+  </si>
+  <si>
+    <t>中邮理财平衡策略</t>
+  </si>
+  <si>
+    <t>932046</t>
+  </si>
+  <si>
+    <t>建行科技（长三角）</t>
+  </si>
+  <si>
+    <t>950076</t>
+  </si>
+  <si>
+    <t>50两倍</t>
+  </si>
+  <si>
+    <t>950077</t>
+  </si>
+  <si>
+    <t>50反向</t>
+  </si>
+  <si>
+    <t>950078</t>
+  </si>
+  <si>
+    <t>50反两</t>
+  </si>
+  <si>
+    <t>H30076</t>
+  </si>
+  <si>
+    <t>期指两倍</t>
+  </si>
+  <si>
+    <t>H30077</t>
+  </si>
+  <si>
+    <t>期指反向</t>
+  </si>
+  <si>
+    <t>H30078</t>
+  </si>
+  <si>
+    <t>期指反两</t>
+  </si>
+  <si>
+    <t>H30082</t>
+  </si>
+  <si>
+    <t>300两倍</t>
+  </si>
+  <si>
+    <t>H30083</t>
+  </si>
+  <si>
+    <t>300反向</t>
+  </si>
+  <si>
+    <t>H30084</t>
+  </si>
+  <si>
+    <t>300反两</t>
+  </si>
+  <si>
+    <t>H30373</t>
+  </si>
+  <si>
+    <t>百发100</t>
+  </si>
+  <si>
+    <t>H30403</t>
+  </si>
+  <si>
+    <t>300日报酬两倍</t>
+  </si>
+  <si>
+    <t>H30404</t>
+  </si>
+  <si>
+    <t>300日报酬反向</t>
+  </si>
+  <si>
+    <t>H30537</t>
+  </si>
+  <si>
+    <t>淘金100</t>
+  </si>
+  <si>
+    <t>H50045</t>
+  </si>
+  <si>
+    <t>180两倍</t>
+  </si>
+  <si>
+    <t>H50046</t>
+  </si>
+  <si>
+    <t>180反向</t>
   </si>
   <si>
     <t>H50047</t>
   </si>
   <si>
     <t>180反两</t>
-  </si>
-  <si>
-    <t>SH</t>
-  </si>
-  <si>
-    <t>H50046</t>
-  </si>
-  <si>
-    <t>180反向</t>
-  </si>
-  <si>
-    <t>H50045</t>
-  </si>
-  <si>
-    <t>180两倍</t>
-  </si>
-  <si>
-    <t>H30084</t>
-  </si>
-  <si>
-    <t>300反两</t>
-  </si>
-  <si>
-    <t>H30083</t>
-  </si>
-  <si>
-    <t>300反向</t>
-  </si>
-  <si>
-    <t>H30082</t>
-  </si>
-  <si>
-    <t>300两倍</t>
-  </si>
-  <si>
-    <t>H30404</t>
-  </si>
-  <si>
-    <t>300日报酬反向</t>
-  </si>
-  <si>
-    <t>H30403</t>
-  </si>
-  <si>
-    <t>300日报酬两倍</t>
-  </si>
-  <si>
-    <t>930734</t>
-  </si>
-  <si>
-    <t>360互联+</t>
-  </si>
-  <si>
-    <t>主题</t>
-  </si>
-  <si>
-    <t>930657</t>
-  </si>
-  <si>
-    <t>500反两</t>
-  </si>
-  <si>
-    <t>930656</t>
-  </si>
-  <si>
-    <t>500反向</t>
-  </si>
-  <si>
-    <t>930655</t>
-  </si>
-  <si>
-    <t>500两倍</t>
-  </si>
-  <si>
-    <t>950078</t>
-  </si>
-  <si>
-    <t>50反两</t>
-  </si>
-  <si>
-    <t>950077</t>
-  </si>
-  <si>
-    <t>50反向</t>
-  </si>
-  <si>
-    <t>950076</t>
-  </si>
-  <si>
-    <t>50两倍</t>
-  </si>
-  <si>
-    <t>930715</t>
-  </si>
-  <si>
-    <t>CS朝阳88</t>
-  </si>
-  <si>
-    <t>H30373</t>
-  </si>
-  <si>
-    <t>百发100</t>
-  </si>
-  <si>
-    <t>930994</t>
-  </si>
-  <si>
-    <t>工银股混</t>
-  </si>
-  <si>
-    <t>932046</t>
-  </si>
-  <si>
-    <t>建行科技（长三角）</t>
-  </si>
-  <si>
-    <t>931240</t>
-  </si>
-  <si>
-    <t>金选偏股基金</t>
-  </si>
-  <si>
-    <t>880880</t>
-  </si>
-  <si>
-    <t>近期强势</t>
-  </si>
-  <si>
-    <t>风格</t>
-  </si>
-  <si>
-    <t>TDXBLK</t>
-  </si>
-  <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>880881</t>
-  </si>
-  <si>
-    <t>近期弱势</t>
-  </si>
-  <si>
-    <t>880866</t>
-  </si>
-  <si>
-    <t>近期新低</t>
-  </si>
-  <si>
-    <t>880865</t>
-  </si>
-  <si>
-    <t>近期新高</t>
-  </si>
-  <si>
-    <t>H30078</t>
-  </si>
-  <si>
-    <t>期指反两</t>
-  </si>
-  <si>
-    <t>H30077</t>
-  </si>
-  <si>
-    <t>期指反向</t>
-  </si>
-  <si>
-    <t>H30076</t>
-  </si>
-  <si>
-    <t>期指两倍</t>
-  </si>
-  <si>
-    <t>931376</t>
-  </si>
-  <si>
-    <t>泰康红利LV</t>
-  </si>
-  <si>
-    <t>H30537</t>
-  </si>
-  <si>
-    <t>淘金100</t>
-  </si>
-  <si>
-    <t>931228</t>
-  </si>
-  <si>
-    <t>亚洲新兴市场科技</t>
-  </si>
-  <si>
-    <t>931563</t>
-  </si>
-  <si>
-    <t>银华配置</t>
-  </si>
-  <si>
-    <t>931659</t>
-  </si>
-  <si>
-    <t>中邮理财平衡策略</t>
-  </si>
-  <si>
-    <t>931658</t>
-  </si>
-  <si>
-    <t>中邮理财稳健策略</t>
-  </si>
-  <si>
-    <t>930903</t>
-  </si>
-  <si>
-    <t>中证A股</t>
-  </si>
-  <si>
-    <t>综合</t>
-  </si>
-  <si>
-    <t>000902</t>
-  </si>
-  <si>
-    <t>中证流通</t>
-  </si>
-  <si>
-    <t>000985</t>
-  </si>
-  <si>
-    <t>中证全指</t>
-  </si>
-  <si>
-    <t>规模</t>
-  </si>
-  <si>
-    <t>880785</t>
-  </si>
-  <si>
-    <t>最近多板</t>
-  </si>
-  <si>
-    <t>880699</t>
-  </si>
-  <si>
-    <t>最近情绪</t>
-  </si>
-  <si>
-    <t>880884</t>
-  </si>
-  <si>
-    <t>最近异动</t>
-  </si>
-  <si>
-    <t>880752</t>
-  </si>
-  <si>
-    <t>昨曾跌停</t>
-  </si>
-  <si>
-    <t>880874</t>
-  </si>
-  <si>
-    <t>昨曾涨停</t>
-  </si>
-  <si>
-    <t>880789</t>
-  </si>
-  <si>
-    <t>昨成交20</t>
-  </si>
-  <si>
-    <t>880751</t>
-  </si>
-  <si>
-    <t>昨日跌停</t>
-  </si>
-  <si>
-    <t>880812</t>
-  </si>
-  <si>
-    <t>昨日连板</t>
-  </si>
-  <si>
-    <t>880770</t>
-  </si>
-  <si>
-    <t>昨日上榜</t>
-  </si>
-  <si>
-    <t>880774</t>
-  </si>
-  <si>
-    <t>昨日首板</t>
-  </si>
-  <si>
-    <t>880863</t>
-  </si>
-  <si>
-    <t>昨日涨停</t>
   </si>
 </sst>
 </file>
@@ -396,14 +396,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -881,158 +874,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1384,7 +1377,14 @@
   <dimension ref="A1:H51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
     <col min="2" max="2" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="5.375" customWidth="1"/>
+    <col min="5" max="5" width="7.375" customWidth="1"/>
+    <col min="6" max="6" width="8.125" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1424,7 +1424,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>4988</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -1447,10 +1447,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>4866</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1466,407 +1466,407 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4">
-        <v>62</v>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1">
+        <v>181</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>180</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="D5" s="1">
+        <v>40</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H5">
-        <v>62</v>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="G6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>180</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1">
+        <v>49</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H6">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>180</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="F7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1">
+        <v>59</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H7">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>300</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8">
-        <v>62</v>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>300</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9">
-        <v>62</v>
+      <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1">
+        <v>44</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10">
-        <v>300</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10">
-        <v>62</v>
+      <c r="A10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <v>300</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11">
-        <v>62</v>
+      <c r="A11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1">
+        <v>81</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1">
+        <v>217</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1">
+        <v>84</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1">
         <v>33</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <v>300</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>500</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15">
-        <v>500</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15">
-        <v>62</v>
+      <c r="E15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16">
-        <v>500</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16">
-        <v>62</v>
+      <c r="A16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1">
+        <v>64</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17">
+      <c r="A17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1">
+        <v>83</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1">
+        <v>70</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H17">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18">
-        <v>50</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18">
-        <v>62</v>
+      <c r="F18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D19">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -1875,7 +1875,7 @@
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H19">
         <v>62</v>
@@ -1883,16 +1883,16 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D20">
-        <v>88</v>
+        <v>500</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -1909,16 +1909,16 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
         <v>53</v>
       </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
       <c r="D21">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -1935,16 +1935,16 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D22">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -1961,16 +1961,16 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D23">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
@@ -1987,143 +1987,143 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24">
+        <v>100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26">
+        <v>100</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
         <v>10</v>
       </c>
-      <c r="D24">
-        <v>112</v>
-      </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="1">
-        <v>64</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="1">
-        <v>83</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="1">
-        <v>84</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1</v>
+      <c r="D27">
+        <v>4988</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="1">
-        <v>217</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="1">
-        <v>1</v>
+      <c r="A28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28">
+        <v>30</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -2143,16 +2143,16 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s">
         <v>11</v>
@@ -2169,16 +2169,16 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
@@ -2195,16 +2195,16 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
         <v>11</v>
@@ -2221,16 +2221,16 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D33">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
@@ -2247,16 +2247,16 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
         <v>11</v>
@@ -2273,16 +2273,16 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D35">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E35" t="s">
         <v>11</v>
@@ -2299,16 +2299,16 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D36">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
         <v>11</v>
@@ -2317,7 +2317,7 @@
         <v>12</v>
       </c>
       <c r="G36" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H36">
         <v>62</v>
@@ -2325,16 +2325,16 @@
     </row>
     <row r="37" s="1" customFormat="1" spans="1:8">
       <c r="A37" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D37">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E37" t="s">
         <v>11</v>
@@ -2343,7 +2343,7 @@
         <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H37">
         <v>62</v>
@@ -2351,16 +2351,16 @@
     </row>
     <row r="38" s="1" customFormat="1" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="D38">
-        <v>4988</v>
+        <v>50</v>
       </c>
       <c r="E38" t="s">
         <v>11</v>
@@ -2369,7 +2369,7 @@
         <v>12</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H38">
         <v>62</v>
@@ -2377,16 +2377,16 @@
     </row>
     <row r="39" s="1" customFormat="1" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="D39">
-        <v>4988</v>
+        <v>2</v>
       </c>
       <c r="E39" t="s">
         <v>11</v>
@@ -2403,16 +2403,16 @@
     </row>
     <row r="40" s="1" customFormat="1" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="D40">
-        <v>4866</v>
+        <v>2</v>
       </c>
       <c r="E40" t="s">
         <v>11</v>
@@ -2428,294 +2428,294 @@
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:8">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="1">
-        <v>44</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="1">
-        <v>1</v>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41">
+        <v>62</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:8">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" s="1">
-        <v>181</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="1">
-        <v>1</v>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42">
+        <v>300</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42">
+        <v>62</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:8">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" s="1">
-        <v>70</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="1">
-        <v>1</v>
+      <c r="C43" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43">
+        <v>300</v>
+      </c>
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43">
+        <v>62</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:8">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="1">
-        <v>24</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H44" s="1">
-        <v>1</v>
+      <c r="C44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44">
+        <v>300</v>
+      </c>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44">
+        <v>62</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:8">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>106</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" s="1">
-        <v>33</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="1">
-        <v>1</v>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45">
+        <v>100</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45">
+        <v>62</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:8">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>108</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" s="1">
-        <v>20</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="1">
-        <v>1</v>
+      <c r="C46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46">
+        <v>300</v>
+      </c>
+      <c r="E46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46">
+        <v>62</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:8">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
         <v>110</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D47" s="1">
-        <v>40</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" s="1">
-        <v>1</v>
+      <c r="C47" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47">
+        <v>300</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47">
+        <v>62</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:8">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>112</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="1">
-        <v>13</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H48" s="1">
-        <v>1</v>
+      <c r="C48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48">
+        <v>100</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48">
+        <v>62</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:8">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" s="1">
-        <v>49</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H49" s="1">
-        <v>1</v>
+      <c r="C49" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49">
+        <v>180</v>
+      </c>
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49">
+        <v>62</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:8">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>116</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="1">
-        <v>59</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H50" s="1">
-        <v>1</v>
+      <c r="C50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50">
+        <v>180</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50">
+        <v>62</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:8">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" s="1">
-        <v>81</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H51" s="1">
-        <v>1</v>
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51">
+        <v>180</v>
+      </c>
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:H71">
-    <sortCondition ref="B2"/>
+  <sortState ref="A2:H51">
+    <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
